--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118843728</v>
+        <v>118843715</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118843299</v>
+        <v>118843669</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504035</v>
+        <v>504135</v>
       </c>
       <c r="R3" t="n">
-        <v>6818779</v>
+        <v>6818909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118843669</v>
+        <v>118843728</v>
       </c>
       <c r="B4" t="n">
         <v>78484</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504135</v>
+        <v>504136</v>
       </c>
       <c r="R4" t="n">
-        <v>6818909</v>
+        <v>6818897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118843715</v>
+        <v>118843299</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504136</v>
+        <v>504035</v>
       </c>
       <c r="R5" t="n">
-        <v>6818897</v>
+        <v>6818779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118843715</v>
+        <v>118843669</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504136</v>
+        <v>504135</v>
       </c>
       <c r="R2" t="n">
-        <v>6818897</v>
+        <v>6818909</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118843669</v>
+        <v>118843241</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504135</v>
+        <v>504026</v>
       </c>
       <c r="R3" t="n">
-        <v>6818909</v>
+        <v>6818786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118843728</v>
+        <v>118843299</v>
       </c>
       <c r="B4" t="n">
         <v>78484</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504136</v>
+        <v>504035</v>
       </c>
       <c r="R4" t="n">
-        <v>6818897</v>
+        <v>6818779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118843299</v>
+        <v>118843728</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504035</v>
+        <v>504136</v>
       </c>
       <c r="R5" t="n">
-        <v>6818779</v>
+        <v>6818897</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118843241</v>
+        <v>118843715</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504026</v>
+        <v>504136</v>
       </c>
       <c r="R6" t="n">
-        <v>6818786</v>
+        <v>6818897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118843669</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118843241</v>
+        <v>118843728</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504026</v>
+        <v>504136</v>
       </c>
       <c r="R3" t="n">
-        <v>6818786</v>
+        <v>6818897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>118843299</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118843728</v>
+        <v>118843241</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504136</v>
+        <v>504026</v>
       </c>
       <c r="R5" t="n">
-        <v>6818897</v>
+        <v>6818786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>118843715</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118843728</v>
+        <v>118843715</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118843715</v>
+        <v>118843728</v>
       </c>
       <c r="B6" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118843728</v>
+        <v>118843241</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källbäcken (Källbäcken), Dlr</t>
+          <t>Källbäcken, Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504136</v>
+        <v>504026</v>
       </c>
       <c r="R2" t="n">
-        <v>6818897</v>
+        <v>6818786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118843715</v>
+        <v>118843299</v>
       </c>
       <c r="B3" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källbäcken (Källbäcken), Dlr</t>
+          <t>Källbäcken, Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504136</v>
+        <v>504035</v>
       </c>
       <c r="R3" t="n">
-        <v>6818897</v>
+        <v>6818779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118843299</v>
+        <v>118843389</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -935,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källbäcken (Källbäcken), Dlr</t>
+          <t>Källbäcken, Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504035</v>
+        <v>504078</v>
       </c>
       <c r="R4" t="n">
-        <v>6818779</v>
+        <v>6818828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118843669</v>
+        <v>118843396</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1047,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källbäcken (Källbäcken), Dlr</t>
+          <t>Källbäcken, Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504135</v>
+        <v>504098</v>
       </c>
       <c r="R5" t="n">
-        <v>6818909</v>
+        <v>6818825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118843241</v>
+        <v>118843669</v>
       </c>
       <c r="B6" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1159,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källbäcken (Källbäcken), Dlr</t>
+          <t>Källbäcken, Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504026</v>
+        <v>504135</v>
       </c>
       <c r="R6" t="n">
-        <v>6818786</v>
+        <v>6818909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1207,439 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118843728</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källbäcken, Källbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504136</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6818897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118844429</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källbäcken, Källbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504197</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6819109</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118843715</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källbäcken, Källbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6818897</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118843336</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Källbäcken, Källbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504078</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6818786</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28422-2024 artfynd.xlsx
+++ b/artfynd/A 28422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843389</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843669</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843728</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118844429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843715</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,8 +1685,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843336</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>